--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty 100 Low Volatility 30 ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty 100 Low Volatility 30 ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="117">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty 100 Low Volatility 30 ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -70,13 +70,154 @@
     <t>Food Products</t>
   </si>
   <si>
+    <t>Britannia Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE216A01030</t>
+  </si>
+  <si>
+    <t>ICICI Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE090A01021</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE040A01034</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Reliance Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE002A01018</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
     <t>Hindustan Unilever Ltd.</t>
   </si>
   <si>
     <t>INE030A01027</t>
   </si>
   <si>
-    <t>Diversified Fmcg</t>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Sun Pharmaceutical Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE044A01036</t>
+  </si>
+  <si>
+    <t>Titan Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE280A01028</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Hero Motocorp Ltd.</t>
+  </si>
+  <si>
+    <t>INE158A01026</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>Apollo Hospitals Enterprise Ltd.</t>
+  </si>
+  <si>
+    <t>INE437A01024</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
+    <t>Asian Paints Ltd.</t>
+  </si>
+  <si>
+    <t>INE021A01026</t>
+  </si>
+  <si>
+    <t>Maruti Suzuki India Ltd.</t>
+  </si>
+  <si>
+    <t>INE585B01010</t>
+  </si>
+  <si>
+    <t>Bosch Ltd.</t>
+  </si>
+  <si>
+    <t>INE323A01026</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Tata Consultancy Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE467B01029</t>
+  </si>
+  <si>
+    <t>It - Software</t>
+  </si>
+  <si>
+    <t>Pidilite Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE318A01026</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
+    <t>HCL Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE860A01027</t>
   </si>
   <si>
     <t>Bajaj Finserv Ltd.</t>
@@ -88,76 +229,37 @@
     <t>Finance</t>
   </si>
   <si>
-    <t>Maruti Suzuki India Ltd.</t>
-  </si>
-  <si>
-    <t>INE585B01010</t>
-  </si>
-  <si>
-    <t>Automobiles</t>
-  </si>
-  <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
-  </si>
-  <si>
-    <t>Sun Pharmaceutical Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE044A01036</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
-  </si>
-  <si>
-    <t>Asian Paints Ltd.</t>
-  </si>
-  <si>
-    <t>INE021A01026</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Tata Consultancy Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE467B01029</t>
-  </si>
-  <si>
-    <t>It - Software</t>
-  </si>
-  <si>
-    <t>Reliance Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE002A01018</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>ICICI Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE090A01021</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>Titan Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE280A01028</t>
+    <t>Infosys Ltd.</t>
+  </si>
+  <si>
+    <t>INE009A01021</t>
+  </si>
+  <si>
+    <t>Cipla Ltd.</t>
+  </si>
+  <si>
+    <t>INE059A01026</t>
+  </si>
+  <si>
+    <t>Ultratech Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE481G01011</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Bajaj Auto Ltd.</t>
+  </si>
+  <si>
+    <t>INE917I01010</t>
+  </si>
+  <si>
+    <t>Torrent Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE685A01028</t>
   </si>
   <si>
     <t>Kotak Mahindra Bank Ltd.</t>
@@ -166,60 +268,6 @@
     <t>INE237A01028</t>
   </si>
   <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>Dr. Reddy's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE089A01031</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>Ultratech Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE481G01011</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>Apollo Hospitals Enterprise Ltd.</t>
-  </si>
-  <si>
-    <t>INE437A01024</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE040A01034</t>
-  </si>
-  <si>
-    <t>Infosys Ltd.</t>
-  </si>
-  <si>
-    <t>INE009A01021</t>
-  </si>
-  <si>
     <t>Dabur India Ltd.</t>
   </si>
   <si>
@@ -229,37 +277,13 @@
     <t>Personal Products</t>
   </si>
   <si>
-    <t>Hero Motocorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE158A01026</t>
-  </si>
-  <si>
-    <t>Cipla Ltd.</t>
-  </si>
-  <si>
-    <t>INE059A01026</t>
-  </si>
-  <si>
-    <t>HCL Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE860A01027</t>
-  </si>
-  <si>
-    <t>Pidilite Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE318A01026</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>Torrent Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE685A01028</t>
+    <t>Larsen &amp; Toubro Ltd.</t>
+  </si>
+  <si>
+    <t>INE018A01030</t>
+  </si>
+  <si>
+    <t>Construction</t>
   </si>
   <si>
     <t>Wipro Ltd.</t>
@@ -268,39 +292,6 @@
     <t>INE075A01022</t>
   </si>
   <si>
-    <t>Bajaj Auto Ltd.</t>
-  </si>
-  <si>
-    <t>INE917I01010</t>
-  </si>
-  <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>Bosch Ltd.</t>
-  </si>
-  <si>
-    <t>INE323A01026</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -355,9 +346,6 @@
     <t>Name of the Instrument</t>
   </si>
   <si>
-    <t>Dr. Reddys Laboratories Ltd.</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
@@ -367,7 +355,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -377,9 +365,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - Nifty 100 Low Volatility 30 TRI</t>
   </si>
 </sst>
 </file>
@@ -605,7 +590,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -698,9 +683,6 @@
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -797,13 +779,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -821,7 +803,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="16459200"/>
+          <a:off x="666750" y="16268700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -836,13 +818,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>108</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -860,7 +842,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="19316700"/>
+          <a:off x="666750" y="19126200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1194,19 +1176,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J98"/>
+  <dimension ref="B1:J96"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="27" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="27" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="27" width="16.857142857142858" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="27" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="27" width="34.142857142857146" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="27" width="10.857142857142858" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="27" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="27" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="27" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="27" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="26" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="26" width="53.57142857142857" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="26" width="16.857142857142858" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="26" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="26" width="34.142857142857146" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="26" width="10.857142857142858" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="26" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="26" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="26" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="26" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1294,10 +1276,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>350685.40</v>
+        <v>367484.29000000004</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9987487318424999</v>
+        <v>0.9990677886195001</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1331,10 +1313,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>350685.40</v>
+        <v>367484.29000000004</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9987487318424999</v>
+        <v>0.9990677886195001</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1357,13 +1339,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>629082</v>
+        <v>617444</v>
       </c>
       <c r="G8" s="15">
-        <v>14551.92</v>
+        <v>14795.19</v>
       </c>
       <c r="H8" s="16">
-        <v>0.041443731749</v>
+        <v>0.040223209965</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1383,16 +1365,16 @@
         <v>13</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>576099</v>
+        <v>264611</v>
       </c>
       <c r="G9" s="15">
-        <v>14222.73</v>
+        <v>14581.39</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0405062017148</v>
+        <v>0.0396419587414</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1403,25 +1385,25 @@
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1">
       <c r="B10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="D10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="F10" s="14">
-        <v>775898</v>
+        <v>1005461</v>
       </c>
       <c r="G10" s="15">
-        <v>13470.37</v>
+        <v>14536.96</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0383634874875</v>
+        <v>0.0395211683211</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1432,25 +1414,25 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1">
       <c r="B11" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>26</v>
-      </c>
       <c r="F11" s="14">
-        <v>108909</v>
+        <v>3442046</v>
       </c>
       <c r="G11" s="15">
-        <v>13407.41</v>
+        <v>14389.47</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0381841779977</v>
+        <v>0.0391201919742</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1461,25 +1443,25 @@
     </row>
     <row r="12" spans="2:10" ht="15" customHeight="1">
       <c r="B12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>28</v>
-      </c>
       <c r="D12" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F12" s="14">
-        <v>259707</v>
+        <v>733534</v>
       </c>
       <c r="G12" s="15">
-        <v>13322.06</v>
+        <v>14266.50</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0379411019978</v>
+        <v>0.0387858773673</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1490,25 +1472,25 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>31</v>
-      </c>
       <c r="F13" s="14">
-        <v>762290</v>
+        <v>1117813</v>
       </c>
       <c r="G13" s="15">
-        <v>13293.96</v>
+        <v>13986.08</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0378610734612</v>
+        <v>0.0380235084799</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1519,25 +1501,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>34</v>
-      </c>
       <c r="F14" s="14">
-        <v>567643</v>
+        <v>970659</v>
       </c>
       <c r="G14" s="15">
-        <v>13060.33</v>
+        <v>13792.09</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0371956974113</v>
+        <v>0.0374961140699</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1548,25 +1530,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>36</v>
-      </c>
       <c r="D15" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F15" s="14">
-        <v>2872415</v>
+        <v>585397</v>
       </c>
       <c r="G15" s="15">
-        <v>12854.06</v>
+        <v>13746.88</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0366082423849</v>
+        <v>0.0373732030885</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1577,25 +1559,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="D16" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>39</v>
-      </c>
       <c r="F16" s="14">
-        <v>302369</v>
+        <v>730295</v>
       </c>
       <c r="G16" s="15">
-        <v>12434.62</v>
+        <v>13234.41</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0354136811967</v>
+        <v>0.0359799672862</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1606,25 +1588,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>41</v>
-      </c>
       <c r="D17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F17" s="14">
-        <v>980419</v>
+        <v>783122</v>
       </c>
       <c r="G17" s="15">
-        <v>12403.28</v>
+        <v>13137.65</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0353244251705</v>
+        <v>0.0357169089682</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1635,25 +1617,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>45</v>
-      </c>
       <c r="F18" s="14">
-        <v>977798</v>
+        <v>366780</v>
       </c>
       <c r="G18" s="15">
-        <v>12249.85</v>
+        <v>13039.03</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0348874579688</v>
+        <v>0.0354487939276</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1664,25 +1646,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>34</v>
-      </c>
       <c r="F19" s="14">
-        <v>350740</v>
+        <v>301075</v>
       </c>
       <c r="G19" s="15">
-        <v>12241.70</v>
+        <v>12974.22</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0348642468452</v>
+        <v>0.035272597053</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1693,25 +1675,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="D20" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>45</v>
-      </c>
       <c r="F20" s="14">
-        <v>643425</v>
+        <v>181993</v>
       </c>
       <c r="G20" s="15">
-        <v>12233.44</v>
+        <v>12522.03</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0348407224426</v>
+        <v>0.0340432425591</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1734,13 +1716,13 @@
         <v>52</v>
       </c>
       <c r="F21" s="14">
-        <v>741075</v>
+        <v>668611</v>
       </c>
       <c r="G21" s="15">
-        <v>12052.10</v>
+        <v>12410.76</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0343242678225</v>
+        <v>0.033740736368</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1760,16 +1742,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F22" s="14">
-        <v>977214</v>
+        <v>546553</v>
       </c>
       <c r="G22" s="15">
-        <v>11896.11</v>
+        <v>12347.18</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0338800097648</v>
+        <v>0.0335678834551</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1789,16 +1771,16 @@
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F23" s="14">
-        <v>779522</v>
+        <v>98612</v>
       </c>
       <c r="G23" s="15">
-        <v>11564.99</v>
+        <v>12148.01</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0329369831087</v>
+        <v>0.0330264063447</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1809,25 +1791,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="D24" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>60</v>
-      </c>
       <c r="F24" s="14">
-        <v>100615</v>
+        <v>38580</v>
       </c>
       <c r="G24" s="15">
-        <v>11558.10</v>
+        <v>12119.91</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0329173604533</v>
+        <v>0.0329500117732</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1838,25 +1820,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="D25" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="F25" s="14">
-        <v>166448</v>
+        <v>347602</v>
       </c>
       <c r="G25" s="15">
-        <v>11335.94</v>
+        <v>12038.85</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0322846508558</v>
+        <v>0.0327296365432</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1867,25 +1849,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="D26" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>45</v>
-      </c>
       <c r="F26" s="14">
-        <v>662695</v>
+        <v>375090</v>
       </c>
       <c r="G26" s="15">
-        <v>11257.53</v>
+        <v>11654.80</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0320613399109</v>
+        <v>0.0316855320885</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1905,16 +1887,16 @@
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F27" s="14">
-        <v>596985</v>
+        <v>704510</v>
       </c>
       <c r="G27" s="15">
-        <v>11222.12</v>
+        <v>11530.01</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0319604925628</v>
+        <v>0.0313462695057</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1937,13 +1919,13 @@
         <v>70</v>
       </c>
       <c r="F28" s="14">
-        <v>2073102</v>
+        <v>568893</v>
       </c>
       <c r="G28" s="15">
-        <v>10984.33</v>
+        <v>11476.85</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0312832688719</v>
+        <v>0.0312017451136</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1963,16 +1945,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F29" s="14">
-        <v>243589</v>
+        <v>720317</v>
       </c>
       <c r="G29" s="15">
-        <v>10569.69</v>
+        <v>11256.39</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0301023780387</v>
+        <v>0.0306023875609</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -1992,16 +1974,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F30" s="14">
-        <v>710425</v>
+        <v>746444</v>
       </c>
       <c r="G30" s="15">
-        <v>10510.03</v>
+        <v>10940.63</v>
       </c>
       <c r="H30" s="16">
-        <v>0.029932466918</v>
+        <v>0.0297439409456</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2021,16 +2003,16 @@
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="F31" s="14">
-        <v>605972</v>
+        <v>95758</v>
       </c>
       <c r="G31" s="15">
-        <v>10455.74</v>
+        <v>10734.47</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0297778495069</v>
+        <v>0.0291834603457</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2041,25 +2023,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="F32" s="14">
-        <v>357431</v>
+        <v>121645</v>
       </c>
       <c r="G32" s="15">
-        <v>10264.35</v>
+        <v>10469.99</v>
       </c>
       <c r="H32" s="16">
-        <v>0.029232772581</v>
+        <v>0.0284644270267</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2079,16 +2061,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F33" s="14">
-        <v>306356</v>
+        <v>326311</v>
       </c>
       <c r="G33" s="15">
-        <v>10015.08</v>
+        <v>10359.40</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0285228539577</v>
+        <v>0.0281637695299</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2108,16 +2090,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F34" s="14">
-        <v>3062803</v>
+        <v>494318</v>
       </c>
       <c r="G34" s="15">
-        <v>9552.88</v>
+        <v>10255.62</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0272065126904</v>
+        <v>0.0278816261624</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2137,16 +2119,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="F35" s="14">
-        <v>104523</v>
+        <v>2079310</v>
       </c>
       <c r="G35" s="15">
-        <v>9247.99</v>
+        <v>10042.03</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0263381888285</v>
+        <v>0.0273009458591</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2157,25 +2139,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F36" s="14">
-        <v>257273</v>
+        <v>271205</v>
       </c>
       <c r="G36" s="15">
-        <v>9177.96</v>
+        <v>9967.05</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0261387440449</v>
+        <v>0.0270971001306</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2186,25 +2168,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="F37" s="14">
-        <v>30654</v>
+        <v>3496793</v>
       </c>
       <c r="G37" s="15">
-        <v>8806.63</v>
+        <v>8730.44</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0250811996858</v>
+        <v>0.0237351680652</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2215,720 +2197,686 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" ht="15" customHeight="1">
+      <c r="B39" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="13" t="s">
+      <c r="H39" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" ht="15" customHeight="1">
+      <c r="B40" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" ht="15" customHeight="1">
+      <c r="B41" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="14">
-        <v>287269</v>
-      </c>
-      <c r="G38" s="15">
-        <v>468.10</v>
-      </c>
-      <c r="H38" s="16">
-        <v>0.0013331444119</v>
-      </c>
-      <c r="I38" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" ht="15" customHeight="1">
-      <c r="B39" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" ht="15" customHeight="1">
-      <c r="B40" s="7" t="s">
+      <c r="C41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" ht="15" customHeight="1">
+      <c r="B42" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" ht="15" customHeight="1">
+      <c r="B43" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="15" customHeight="1">
+      <c r="B44" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" ht="15" customHeight="1">
+      <c r="B45" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="9" t="s">
+      <c r="C45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="15" customHeight="1">
+      <c r="B46" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15" customHeight="1">
+      <c r="B47" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="H40" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" ht="15" customHeight="1">
-      <c r="B41" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" ht="15" customHeight="1">
-      <c r="B42" s="7" t="s">
+      <c r="C47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" ht="15" customHeight="1">
+      <c r="B48" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="15" customHeight="1">
+      <c r="B49" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" ht="15" customHeight="1">
-      <c r="B43" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" ht="15" customHeight="1">
-      <c r="B44" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J44" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" ht="15" customHeight="1">
-      <c r="B46" s="7" t="s">
+      <c r="C49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="15" customHeight="1">
+      <c r="B50" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" ht="15" customHeight="1">
+      <c r="B51" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" ht="15" customHeight="1">
-      <c r="B48" s="7" t="s">
+      <c r="C51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" ht="15" customHeight="1">
+      <c r="B52" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" ht="15" customHeight="1">
+      <c r="B53" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J48" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" ht="15" customHeight="1">
-      <c r="B49" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="7" t="s">
+      <c r="C53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" ht="15" customHeight="1">
+      <c r="B54" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" ht="15" customHeight="1">
+      <c r="B55" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" ht="15" customHeight="1">
-      <c r="B52" s="7" t="s">
+      <c r="C55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" ht="15" customHeight="1">
+      <c r="B56" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" ht="15" customHeight="1">
+      <c r="B57" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" ht="15" customHeight="1">
-      <c r="B53" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="7" t="s">
+      <c r="C57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" ht="15" customHeight="1">
+      <c r="B58" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="15" customHeight="1">
+      <c r="B59" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" ht="15" customHeight="1">
-      <c r="B55" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" ht="15" customHeight="1">
-      <c r="B56" s="7" t="s">
+      <c r="C59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" ht="15" customHeight="1">
+      <c r="B60" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" ht="15" customHeight="1">
+      <c r="B61" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H56" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" ht="15" customHeight="1">
-      <c r="B57" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" ht="15" customHeight="1">
-      <c r="B58" s="7" t="s">
+      <c r="C61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" ht="15" customHeight="1">
+      <c r="B62" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" ht="15" customHeight="1">
+      <c r="B63" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" ht="15" customHeight="1">
-      <c r="B59" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J59" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" ht="15" customHeight="1">
-      <c r="B60" s="7" t="s">
+      <c r="C63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="15" customHeight="1">
+      <c r="B64" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" ht="15" customHeight="1">
+      <c r="B65" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C60" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H60" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J60" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" ht="15" customHeight="1">
-      <c r="B61" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" ht="15" customHeight="1">
-      <c r="B62" s="7" t="s">
+      <c r="C65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="9">
+        <v>29.38</v>
+      </c>
+      <c r="H65" s="10">
+        <v>0.0000798744665</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="15" customHeight="1">
+      <c r="B66" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" ht="15" customHeight="1">
+      <c r="B67" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C62" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10" ht="15" customHeight="1">
-      <c r="B63" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" ht="15" customHeight="1">
-      <c r="B64" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H64" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J64" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" ht="15" customHeight="1">
-      <c r="B65" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" ht="15" customHeight="1">
-      <c r="B66" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="9">
-        <v>21.19</v>
-      </c>
-      <c r="H66" s="10">
-        <v>0.0000603489213</v>
-      </c>
-      <c r="I66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" ht="15" customHeight="1">
-      <c r="B67" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J67" s="11" t="s">
+      <c r="C67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="18">
+        <v>313.51268519996665</v>
+      </c>
+      <c r="H67" s="19">
+        <v>0.0008523369124360836</v>
+      </c>
+      <c r="I67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="18">
+        <v>367827.1826852</v>
+      </c>
+      <c r="H68" s="19">
+        <v>0.999999999998436</v>
+      </c>
+      <c r="I68" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J68" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" ht="15" customHeight="1">
+      <c r="B70" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C70" s="22"/>
+    </row>
+    <row r="71" spans="2:3" ht="15" customHeight="1">
+      <c r="B71" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="C68" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="18">
-        <v>418.16121999995084</v>
-      </c>
-      <c r="H68" s="19">
-        <v>0.001190919234679496</v>
-      </c>
-      <c r="I68" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J68" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" ht="15" customHeight="1">
-      <c r="B69" s="17" t="s">
+      <c r="C71" s="24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" ht="15" customHeight="1">
+      <c r="B72" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C72" s="25">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" ht="15" customHeight="1">
+      <c r="B74" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" s="18">
-        <v>351124.75122</v>
-      </c>
-      <c r="H69" s="19">
-        <v>0.9999999999984795</v>
-      </c>
-      <c r="I69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J69" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="2:3" ht="15" customHeight="1">
-      <c r="B71" s="21" t="s">
+      <c r="C74" s="26"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="26"/>
+    </row>
+    <row r="75" spans="2:8" ht="15" customHeight="1">
+      <c r="B75" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C71" s="22"/>
-    </row>
-    <row r="72" spans="2:3" ht="15" customHeight="1">
-      <c r="B72" s="23" t="s">
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="26"/>
+    </row>
+    <row r="76" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B76" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="C72" s="24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="2:3" ht="15" customHeight="1">
-      <c r="B73" s="25" t="s">
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+    </row>
+    <row r="77" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B77" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="C73" s="26">
-        <v>115744</v>
-      </c>
-    </row>
-    <row r="75" spans="2:9" ht="15" customHeight="1">
-      <c r="B75" s="13" t="s">
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="26"/>
+    </row>
+    <row r="78" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B78" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="C75" s="27"/>
-      <c r="D75" s="27"/>
-      <c r="E75" s="27"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="27"/>
-      <c r="H75" s="27"/>
-      <c r="I75" s="27"/>
-    </row>
-    <row r="76" spans="2:8" ht="15" customHeight="1">
-      <c r="B76" s="13" t="s">
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+    </row>
+    <row r="81" ht="15">
+      <c r="B81" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="C76" s="27"/>
-      <c r="D76" s="27"/>
-      <c r="E76" s="27"/>
-      <c r="F76" s="27"/>
-      <c r="G76" s="27"/>
-      <c r="H76" s="27"/>
-    </row>
-    <row r="77" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B77" s="28" t="s">
+    </row>
+    <row r="96" ht="15">
+      <c r="B96" s="26" t="s">
         <v>116</v>
-      </c>
-      <c r="C77" s="27"/>
-      <c r="D77" s="27"/>
-      <c r="E77" s="27"/>
-      <c r="F77" s="27"/>
-      <c r="G77" s="27"/>
-      <c r="H77" s="27"/>
-    </row>
-    <row r="78" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B78" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="27"/>
-      <c r="H78" s="27"/>
-    </row>
-    <row r="79" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B79" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="C79" s="27"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="27"/>
-      <c r="H79" s="27"/>
-    </row>
-    <row r="82" ht="15">
-      <c r="B82" s="27" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="97" ht="15">
-      <c r="B97" s="27" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="98" ht="15">
-      <c r="B98" s="27" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B76:H76"/>
     <mergeCell ref="B77:H77"/>
     <mergeCell ref="B78:H78"/>
-    <mergeCell ref="B79:H79"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B75:I75"/>
-    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B75:H75"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
